--- a/WorkBot/refactor/data/orders/Coca-Cola/Coca-Cola_Downtown_2025-10-17.xlsx
+++ b/WorkBot/refactor/data/orders/Coca-Cola/Coca-Cola_Downtown_2025-10-17.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,6 +578,87 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>156184</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Core Power Protein - Chocolate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>156188</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Core Power Protein - Strawberry</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>156182</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Core Power Protein - Vanilla</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>32.55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
